--- a/templates/ziraat-ek-tablo.xlsx
+++ b/templates/ziraat-ek-tablo.xlsx
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B3" s="113" t="inlineStr">
         <is>
-          <t>{{TASINMAZ_ID}}</t>
+          <t>Sistemden BKNZ</t>
         </is>
       </c>
       <c r="C3" s="113" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D3" s="113" t="inlineStr">
         <is>
-          <t>{{YAPI_RUHSATI}}</t>
+          <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
       <c r="E3" s="113" t="n">
@@ -2655,11 +2655,7 @@
       <c r="A4" s="121" t="n"/>
       <c r="B4" s="122" t="n"/>
       <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="inlineStr">
-        <is>
-          <t>{{ISKAN_BELGESI}}</t>
-        </is>
-      </c>
+      <c r="D4" s="122" t="n"/>
       <c r="E4" s="122" t="n"/>
       <c r="F4" s="123" t="n"/>
       <c r="G4" s="124" t="n"/>
@@ -2763,10 +2759,9 @@
         <f>C3</f>
         <v/>
       </c>
-      <c r="D10" s="118" t="inlineStr">
-        <is>
-          <t>{{YAPI_RUHSATI}}</t>
-        </is>
+      <c r="D10" s="118">
+        <f>D3</f>
+        <v/>
       </c>
       <c r="E10" s="116" t="n">
         <v>0</v>
@@ -2792,11 +2787,7 @@
         <f>C4</f>
         <v/>
       </c>
-      <c r="D11" s="122" t="inlineStr">
-        <is>
-          <t>{{ISKAN_BELGESI}}</t>
-        </is>
-      </c>
+      <c r="D11" s="122" t="n"/>
       <c r="E11" s="122">
         <f>E4</f>
         <v/>
@@ -2973,7 +2964,7 @@
       </c>
       <c r="B3" s="66" t="inlineStr">
         <is>
-          <t>{{TASINMAZ_ID}}</t>
+          <t>Sistemden BKNZ</t>
         </is>
       </c>
       <c r="C3" s="67" t="inlineStr">
@@ -3032,7 +3023,7 @@
       </c>
       <c r="F4" s="60" t="inlineStr">
         <is>
-          <t>{{YAPI_RUHSATI}}</t>
+          <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
       <c r="G4" s="60" t="n">

--- a/templates/ziraat-ek-tablo.xlsx
+++ b/templates/ziraat-ek-tablo.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARLA" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,9 +19,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="162"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -86,21 +94,8 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial Tur"/>
-      <charset val="162"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -119,8 +114,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="48">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -360,30 +361,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -544,17 +521,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -635,7 +601,9 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -646,7 +614,46 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -655,9 +662,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -668,46 +673,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -723,428 +689,380 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1229,7 +1147,7 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>{{YUZOLCUMU}}</t>
+        <t>{{ARSA_ALANI}}</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
@@ -1254,7 +1172,7 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>{{YUZOLCUMU}}</t>
+        <t>{{ARSA_ALANI}}</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
@@ -1270,6 +1188,11 @@
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>{{HMAX}}</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>{{ARSA_ALANI}}</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
@@ -1333,6 +1256,26 @@
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>{{MEVCUT_DEGER}}</t>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>{{ARSA_ALANI}}</t>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <t>{{YASAL_DEGER}}</t>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <t>{{YAPI_ALANI}}</t>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0">
       <text>
         <t>{{MEVCUT_DEGER}}</t>
       </text>
@@ -1611,323 +1554,382 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="1" min="1" max="1"/>
+    <col width="16.42578125" customWidth="1" style="1" min="1" max="1"/>
     <col width="16" customWidth="1" style="1" min="2" max="2"/>
     <col width="13" customWidth="1" style="1" min="3" max="4"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
-    <col width="16.5703125" customWidth="1" style="17" min="6" max="6"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="17.28515625" customWidth="1" style="3" min="6" max="6"/>
     <col width="17.42578125" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" thickBot="1">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>TARLA YASAL DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B1" s="134" t="n"/>
-      <c r="C1" s="134" t="n"/>
-      <c r="D1" s="134" t="n"/>
-      <c r="E1" s="134" t="n"/>
-      <c r="F1" s="134" t="n"/>
-      <c r="G1" s="135" t="n"/>
-    </row>
-    <row r="2" ht="30.75" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="B1" s="120" t="n"/>
+      <c r="C1" s="120" t="n"/>
+      <c r="D1" s="120" t="n"/>
+      <c r="E1" s="120" t="n"/>
+      <c r="F1" s="120" t="n"/>
+      <c r="G1" s="121" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+      <c r="K1" s="85" t="n"/>
+    </row>
+    <row r="2" ht="61.5" customFormat="1" customHeight="1" s="85" thickBot="1">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>PARSEL</t>
         </is>
       </c>
-      <c r="D2" s="45" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>YÜZÖLÇÜM
 (M²)</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>YASAL BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> YASAL DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="G2" s="48" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="112" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="53" t="inlineStr">
+    <row r="3" ht="34.5" customHeight="1">
+      <c r="A3" s="95" t="inlineStr">
+        <is>
+          <t>Sistemden BKNZ</t>
+        </is>
+      </c>
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>{{ADA}}</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="96" t="inlineStr">
         <is>
           <t>{{PARSEL}}</t>
         </is>
       </c>
-      <c r="D3" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="114">
+      <c r="D3" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_AREA}}</t>
+        </is>
+      </c>
+      <c r="E3" s="97">
         <f>F3/D3</f>
         <v/>
       </c>
-      <c r="F3" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="55" t="inlineStr">
-        <is>
-          <t>{{SATIS_KABILIYETI}}</t>
-        </is>
-      </c>
-      <c r="J3" s="136" t="inlineStr">
+      <c r="F3" s="97" t="inlineStr">
+        <is>
+          <t>{{LEGAL_VALUE}}</t>
+        </is>
+      </c>
+      <c r="G3" s="99" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="85" t="n"/>
+      <c r="J3" s="78" t="inlineStr">
         <is>
           <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
         </is>
       </c>
-      <c r="K3" s="137" t="n"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="58" t="n"/>
-      <c r="C4" s="58" t="n"/>
-      <c r="D4" s="57" t="n"/>
-      <c r="E4" s="114">
-        <f>F4/D4</f>
-        <v/>
-      </c>
-      <c r="F4" s="54" t="n"/>
-      <c r="G4" s="56" t="n"/>
-      <c r="J4" s="138" t="n"/>
-      <c r="K4" s="139" t="n"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A5" s="121" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="123" t="n"/>
-      <c r="F5" s="114" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="J5" s="140" t="n"/>
-      <c r="K5" s="141" t="n"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="121" t="n"/>
-      <c r="B6" s="122" t="n"/>
-      <c r="C6" s="122" t="n"/>
-      <c r="D6" s="122" t="n"/>
-      <c r="E6" s="123" t="n"/>
-      <c r="F6" s="114" t="n"/>
-      <c r="G6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A7" s="121" t="n"/>
-      <c r="B7" s="122" t="n"/>
-      <c r="C7" s="122" t="n"/>
-      <c r="D7" s="122" t="n"/>
-      <c r="E7" s="123" t="n"/>
-      <c r="F7" s="114" t="n"/>
-      <c r="G7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" thickBot="1">
-      <c r="A8" s="93" t="inlineStr">
+      <c r="K3" s="122" t="n"/>
+    </row>
+    <row r="4" ht="34.5" customHeight="1">
+      <c r="A4" s="100" t="n"/>
+      <c r="B4" s="101" t="n"/>
+      <c r="C4" s="101" t="n"/>
+      <c r="D4" s="102" t="n"/>
+      <c r="E4" s="97" t="n"/>
+      <c r="F4" s="97" t="n"/>
+      <c r="G4" s="104" t="n"/>
+      <c r="H4" s="85" t="n"/>
+      <c r="I4" s="85" t="n"/>
+      <c r="J4" s="123" t="n"/>
+      <c r="K4" s="124" t="n"/>
+    </row>
+    <row r="5" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A5" s="32" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="85" t="n"/>
+      <c r="J5" s="125" t="n"/>
+      <c r="K5" s="126" t="n"/>
+    </row>
+    <row r="6" ht="34.5" customHeight="1">
+      <c r="A6" s="32" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="85" t="n"/>
+      <c r="I6" s="85" t="n"/>
+      <c r="J6" s="85" t="n"/>
+      <c r="K6" s="85" t="n"/>
+    </row>
+    <row r="7" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A7" s="32" t="n"/>
+      <c r="B7" s="33" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="85" t="n"/>
+      <c r="I7" s="85" t="n"/>
+      <c r="J7" s="85" t="n"/>
+      <c r="K7" s="85" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" thickBot="1">
+      <c r="A8" s="88" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B8" s="134" t="n"/>
-      <c r="C8" s="134" t="n"/>
-      <c r="D8" s="14">
+      <c r="B8" s="120" t="n"/>
+      <c r="C8" s="120" t="n"/>
+      <c r="D8" s="36">
         <f>SUM(D3:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14">
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36">
         <f>SUM(F3:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" thickBot="1"/>
-    <row r="10" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A10" s="83" t="inlineStr">
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="85" t="n"/>
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="n"/>
+      <c r="K8" s="85" t="n"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A9" s="85" t="n"/>
+      <c r="B9" s="85" t="n"/>
+      <c r="C9" s="85" t="n"/>
+      <c r="D9" s="85" t="n"/>
+      <c r="E9" s="85" t="n"/>
+      <c r="F9" s="85" t="n"/>
+      <c r="G9" s="85" t="n"/>
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="85" t="n"/>
+      <c r="J9" s="85" t="n"/>
+      <c r="K9" s="85" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1" thickBot="1">
+      <c r="A10" s="75" t="inlineStr">
         <is>
           <t>TARLA MEVCUT DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B10" s="134" t="n"/>
-      <c r="C10" s="134" t="n"/>
-      <c r="D10" s="134" t="n"/>
-      <c r="E10" s="134" t="n"/>
-      <c r="F10" s="134" t="n"/>
-      <c r="G10" s="135" t="n"/>
-    </row>
-    <row r="11" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="B10" s="120" t="n"/>
+      <c r="C10" s="120" t="n"/>
+      <c r="D10" s="120" t="n"/>
+      <c r="E10" s="120" t="n"/>
+      <c r="F10" s="120" t="n"/>
+      <c r="G10" s="121" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+    </row>
+    <row r="11" ht="70.5" customHeight="1" thickBot="1">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>PARSEL</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>YÜZÖLÇÜM
 (M²)</t>
         </is>
       </c>
-      <c r="E11" s="47" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>MEVCUT BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="F11" s="47" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve"> MEVCUT DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="G11" s="48" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="112">
-        <f>A3</f>
-        <v/>
-      </c>
-      <c r="B12" s="113">
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+      <c r="K11" s="85" t="n"/>
+    </row>
+    <row r="12" ht="34.5" customHeight="1">
+      <c r="A12" s="95" t="inlineStr">
+        <is>
+          <t>Sistemden BKNZ</t>
+        </is>
+      </c>
+      <c r="B12" s="96">
         <f>B3</f>
         <v/>
       </c>
-      <c r="C12" s="113">
+      <c r="C12" s="96">
         <f>C3</f>
         <v/>
       </c>
-      <c r="D12" s="114">
+      <c r="D12" s="97">
         <f>D3</f>
         <v/>
       </c>
-      <c r="E12" s="114">
+      <c r="E12" s="97">
         <f>F12/D12</f>
         <v/>
       </c>
-      <c r="F12" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="55" t="inlineStr">
-        <is>
-          <t>{{SATIS_KABILIYETI}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="A13" s="112">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B13" s="113">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="C13" s="122">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D13" s="123">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E13" s="114">
-        <f>F13/D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="54" t="n"/>
-      <c r="G13" s="56" t="n"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="A14" s="121" t="n"/>
-      <c r="B14" s="122" t="n"/>
-      <c r="C14" s="122" t="n"/>
-      <c r="D14" s="122" t="n"/>
-      <c r="E14" s="123" t="n"/>
-      <c r="F14" s="114" t="n"/>
-      <c r="G14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="A15" s="121" t="n"/>
-      <c r="B15" s="122" t="n"/>
-      <c r="C15" s="122" t="n"/>
-      <c r="D15" s="122" t="n"/>
-      <c r="E15" s="123" t="n"/>
-      <c r="F15" s="114" t="n"/>
-      <c r="G15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A16" s="121" t="n"/>
-      <c r="B16" s="122" t="n"/>
-      <c r="C16" s="122" t="n"/>
-      <c r="D16" s="122" t="n"/>
-      <c r="E16" s="123" t="n"/>
-      <c r="F16" s="114" t="n"/>
-      <c r="G16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" thickBot="1">
-      <c r="A17" s="93" t="inlineStr">
+      <c r="F12" s="97" t="inlineStr">
+        <is>
+          <t>{{CURRENT_VALUE}}</t>
+        </is>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+    </row>
+    <row r="13" ht="34.5" customHeight="1">
+      <c r="A13" s="95" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="101" t="n"/>
+      <c r="D13" s="102" t="n"/>
+      <c r="E13" s="97" t="n"/>
+      <c r="F13" s="97" t="n"/>
+      <c r="G13" s="104" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+      <c r="K13" s="85" t="n"/>
+    </row>
+    <row r="14" ht="34.5" customHeight="1">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+    </row>
+    <row r="15" ht="34.5" customHeight="1">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
+    </row>
+    <row r="16" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" thickBot="1">
+      <c r="A17" s="88" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B17" s="134" t="n"/>
-      <c r="C17" s="134" t="n"/>
-      <c r="D17" s="14">
+      <c r="B17" s="120" t="n"/>
+      <c r="C17" s="120" t="n"/>
+      <c r="D17" s="36">
         <f>SUM(D12:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14">
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36">
         <f>SUM(F12:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="95" t="n"/>
+      <c r="G17" s="37" t="n"/>
+      <c r="H17" s="85" t="n"/>
+      <c r="I17" s="85" t="n"/>
+      <c r="J17" s="85" t="n"/>
+      <c r="K17" s="85" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="84" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1953,587 +1955,687 @@
   <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.42578125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="14.7109375" customWidth="1" style="1" min="1" max="1"/>
     <col width="12.42578125" customWidth="1" style="1" min="2" max="2"/>
     <col width="11.5703125" customWidth="1" style="1" min="3" max="3"/>
     <col width="11.42578125" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="21" bestFit="1" customWidth="1" style="17" min="5" max="5"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
+    <col width="21" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="20.28515625" customWidth="1" style="4" min="6" max="6"/>
     <col width="15.5703125" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="8.42578125" bestFit="1" customWidth="1" style="17" min="8" max="8"/>
+    <col width="8.42578125" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
     <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" style="17" min="10" max="10"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="3" min="10" max="10"/>
     <col width="12.42578125" bestFit="1" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A1" s="101" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" thickBot="1">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>ARSA İMAR VE YAPILAŞMA KOŞULLARI</t>
         </is>
       </c>
-      <c r="B1" s="142" t="n"/>
-      <c r="C1" s="142" t="n"/>
-      <c r="D1" s="142" t="n"/>
-      <c r="E1" s="142" t="n"/>
-      <c r="F1" s="142" t="n"/>
-      <c r="G1" s="142" t="n"/>
-      <c r="H1" s="142" t="n"/>
-      <c r="I1" s="142" t="n"/>
-      <c r="J1" s="142" t="n"/>
-      <c r="K1" s="143" t="n"/>
-    </row>
-    <row r="2" ht="60.75" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="B1" s="127" t="n"/>
+      <c r="C1" s="127" t="n"/>
+      <c r="D1" s="127" t="n"/>
+      <c r="E1" s="127" t="n"/>
+      <c r="F1" s="127" t="n"/>
+      <c r="G1" s="127" t="n"/>
+      <c r="H1" s="127" t="n"/>
+      <c r="I1" s="127" t="n"/>
+      <c r="J1" s="127" t="n"/>
+      <c r="K1" s="128" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+      <c r="N1" s="85" t="n"/>
+      <c r="O1" s="85" t="n"/>
+    </row>
+    <row r="2" ht="121.5" customFormat="1" customHeight="1" s="85" thickBot="1">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>PARSEL</t>
         </is>
       </c>
-      <c r="D2" s="45" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>YÜZÖLÇÜM
 (M²)</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>YAPILAŞMA 
 FONKSİYONU</t>
         </is>
       </c>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>KAKS</t>
         </is>
       </c>
-      <c r="G2" s="45" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>TAKS</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
-        <is>
-          <t>H HAX
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>H MAX
 (METRE)</t>
         </is>
       </c>
-      <c r="I2" s="45" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>HESAPLANAN EMSAL</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">TERK SONRASI
 ARSA BÜYÜKLÜĞÜ </t>
         </is>
       </c>
-      <c r="K2" s="48" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>YAPI NİZAMI</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="53" t="inlineStr">
+    <row r="3" ht="34.5" customHeight="1">
+      <c r="A3" s="95" t="inlineStr">
+        <is>
+          <t>Sistemden BKNZ</t>
+        </is>
+      </c>
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>{{ADA}}</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="96" t="inlineStr">
         <is>
           <t>{{PARSEL}}</t>
         </is>
       </c>
-      <c r="D3" s="54" t="n">
+      <c r="D3" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_AREA}}</t>
+        </is>
+      </c>
+      <c r="E3" s="97" t="inlineStr">
+        <is>
+          <t>{{LEGEND}}</t>
+        </is>
+      </c>
+      <c r="F3" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="54" t="inlineStr">
-        <is>
-          <t>{{YAPILASMA_FONKSIYONU}}</t>
-        </is>
-      </c>
-      <c r="F3" s="73" t="n">
+      <c r="G3" s="96" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="53" t="n">
+      <c r="H3" s="96" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="114">
-        <f>J3*F3</f>
-        <v/>
-      </c>
-      <c r="J3" s="54">
-        <f>D3</f>
-        <v/>
-      </c>
-      <c r="K3" s="55" t="inlineStr">
-        <is>
-          <t>{{YAPI_NIZAMI}}</t>
-        </is>
-      </c>
-      <c r="N3" s="136" t="inlineStr">
-        <is>
-          <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
-        </is>
-      </c>
-      <c r="O3" s="137" t="n"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="58" t="n"/>
-      <c r="C4" s="58" t="n"/>
-      <c r="D4" s="57" t="n"/>
-      <c r="E4" s="57" t="n"/>
-      <c r="F4" s="74" t="n"/>
-      <c r="G4" s="58" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="114">
-        <f>J4*F4</f>
-        <v/>
-      </c>
-      <c r="J4" s="54">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="K4" s="56" t="n"/>
-      <c r="N4" s="138" t="n"/>
-      <c r="O4" s="139" t="n"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A5" s="121" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="123" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="122" t="n"/>
-      <c r="H5" s="123" t="n"/>
-      <c r="I5" s="122" t="n"/>
-      <c r="J5" s="123" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="N5" s="140" t="n"/>
-      <c r="O5" s="141" t="n"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1">
-      <c r="A6" s="121" t="n"/>
-      <c r="B6" s="122" t="n"/>
-      <c r="C6" s="122" t="n"/>
-      <c r="D6" s="122" t="n"/>
-      <c r="E6" s="123" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="122" t="n"/>
-      <c r="H6" s="123" t="n"/>
-      <c r="I6" s="122" t="n"/>
-      <c r="J6" s="123" t="n"/>
-      <c r="K6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" thickBot="1">
-      <c r="A8" s="105" t="inlineStr">
+      <c r="I3" s="119" t="inlineStr">
+        <is>
+          <t>{{CALCULATED_EMSAL}}</t>
+        </is>
+      </c>
+      <c r="J3" s="119" t="inlineStr">
+        <is>
+          <t>{{POST_ROAD_SETBACK_PARCEL_AREA}}</t>
+        </is>
+      </c>
+      <c r="K3" s="99" t="inlineStr">
+        <is>
+          <t>{{ORDER}}</t>
+        </is>
+      </c>
+      <c r="L3" s="85" t="n"/>
+      <c r="M3" s="85" t="n"/>
+    </row>
+    <row r="4" ht="34.5" customHeight="1">
+      <c r="A4" s="100" t="n"/>
+      <c r="B4" s="101" t="n"/>
+      <c r="C4" s="101" t="n"/>
+      <c r="D4" s="102" t="n"/>
+      <c r="E4" s="102" t="n"/>
+      <c r="F4" s="103" t="n"/>
+      <c r="G4" s="101" t="n"/>
+      <c r="H4" s="96" t="n"/>
+      <c r="I4" s="97" t="n"/>
+      <c r="J4" s="97" t="n"/>
+      <c r="K4" s="104" t="n"/>
+      <c r="L4" s="85" t="n"/>
+      <c r="M4" s="85" t="n"/>
+    </row>
+    <row r="5" ht="34.5" customHeight="1">
+      <c r="A5" s="32" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="34" t="n"/>
+      <c r="K5" s="35" t="n"/>
+      <c r="L5" s="85" t="n"/>
+      <c r="M5" s="85" t="n"/>
+    </row>
+    <row r="6" ht="34.5" customHeight="1">
+      <c r="A6" s="32" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="35" t="n"/>
+      <c r="L6" s="85" t="n"/>
+      <c r="M6" s="85" t="n"/>
+    </row>
+    <row r="7" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A7" s="40" t="n"/>
+      <c r="B7" s="41" t="n"/>
+      <c r="C7" s="41" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="43" t="n"/>
+      <c r="G7" s="41" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="41" t="n"/>
+      <c r="J7" s="42" t="n"/>
+      <c r="K7" s="44" t="n"/>
+      <c r="L7" s="85" t="n"/>
+      <c r="M7" s="85" t="n"/>
+      <c r="N7" s="85" t="n"/>
+      <c r="O7" s="85" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" thickBot="1">
+      <c r="A8" s="92" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B8" s="134" t="n"/>
-      <c r="C8" s="135" t="n"/>
-      <c r="D8" s="14">
+      <c r="B8" s="120" t="n"/>
+      <c r="C8" s="121" t="n"/>
+      <c r="D8" s="36">
         <f>SUM(D3:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="106" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="106" t="n"/>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" thickBot="1">
-      <c r="A9" s="18" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="18" t="n"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="45" t="n"/>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="37" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+      <c r="N8" s="85" t="n"/>
+      <c r="O8" s="85" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" thickBot="1">
+      <c r="A9" s="47" t="n"/>
+      <c r="B9" s="47" t="n"/>
+      <c r="C9" s="47" t="n"/>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="47" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="48" t="n"/>
+      <c r="K9" s="47" t="n"/>
+      <c r="L9" s="85" t="n"/>
+      <c r="M9" s="85" t="n"/>
+      <c r="N9" s="85" t="n"/>
+      <c r="O9" s="85" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="89" t="inlineStr">
         <is>
           <t>ARSA YASAL DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B10" s="144" t="n"/>
-      <c r="C10" s="144" t="n"/>
-      <c r="D10" s="144" t="n"/>
-      <c r="E10" s="144" t="n"/>
-      <c r="F10" s="144" t="n"/>
-      <c r="G10" s="145" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="30" customFormat="1" customHeight="1" s="12">
-      <c r="A11" s="79" t="inlineStr">
+      <c r="B10" s="129" t="n"/>
+      <c r="C10" s="129" t="n"/>
+      <c r="D10" s="129" t="n"/>
+      <c r="E10" s="129" t="n"/>
+      <c r="F10" s="129" t="n"/>
+      <c r="G10" s="130" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+      <c r="N10" s="85" t="n"/>
+      <c r="O10" s="85" t="n"/>
+    </row>
+    <row r="11" ht="60" customFormat="1" customHeight="1" s="85">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="C11" s="75" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>PARSEL</t>
         </is>
       </c>
-      <c r="D11" s="76" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>YÜZÖLÇÜM
 (M²)</t>
         </is>
       </c>
-      <c r="E11" s="77" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>YASAL BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="F11" s="78" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve"> YASAL DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="G11" s="80" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="26" t="n"/>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="121">
-        <f>A3</f>
-        <v/>
-      </c>
-      <c r="B12" s="122">
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="34.5" customHeight="1">
+      <c r="A12" s="100" t="inlineStr">
+        <is>
+          <t>Sistemden BKNZ</t>
+        </is>
+      </c>
+      <c r="B12" s="101">
         <f>B3</f>
         <v/>
       </c>
-      <c r="C12" s="122">
+      <c r="C12" s="101">
         <f>C3</f>
         <v/>
       </c>
-      <c r="D12" s="122">
-        <f>D3</f>
-        <v/>
-      </c>
-      <c r="E12" s="123">
+      <c r="D12" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_AREA}}</t>
+        </is>
+      </c>
+      <c r="E12" s="102">
         <f>F12/D12</f>
         <v/>
       </c>
-      <c r="F12" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="56" t="inlineStr">
-        <is>
-          <t>{{SATIS_KABILIYETI}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="A13" s="121">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B13" s="122">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="C13" s="122">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D13" s="122">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E13" s="123">
-        <f>F13/D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="57" t="n"/>
-      <c r="G13" s="56" t="n"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="A14" s="121" t="n"/>
-      <c r="B14" s="122" t="n"/>
-      <c r="C14" s="122" t="n"/>
-      <c r="D14" s="122" t="n"/>
-      <c r="E14" s="123" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="A15" s="121" t="n"/>
-      <c r="B15" s="122" t="n"/>
-      <c r="C15" s="122" t="n"/>
-      <c r="D15" s="122" t="n"/>
-      <c r="E15" s="123" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="A16" s="121" t="n"/>
-      <c r="B16" s="122" t="n"/>
-      <c r="C16" s="122" t="n"/>
-      <c r="D16" s="122" t="n"/>
-      <c r="E16" s="123" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" thickBot="1">
-      <c r="A17" s="96" t="inlineStr">
+      <c r="F12" s="102" t="inlineStr">
+        <is>
+          <t>{{LEGAL_VALUE}}</t>
+        </is>
+      </c>
+      <c r="G12" s="104" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+    </row>
+    <row r="13" ht="34.5" customHeight="1">
+      <c r="A13" s="100" t="n"/>
+      <c r="B13" s="101" t="n"/>
+      <c r="C13" s="101" t="n"/>
+      <c r="D13" s="101" t="n"/>
+      <c r="E13" s="102" t="n"/>
+      <c r="F13" s="102" t="n"/>
+      <c r="G13" s="104" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+      <c r="K13" s="85" t="n"/>
+      <c r="L13" s="85" t="n"/>
+      <c r="M13" s="85" t="n"/>
+      <c r="N13" s="85" t="n"/>
+      <c r="O13" s="85" t="n"/>
+    </row>
+    <row r="14" ht="34.5" customHeight="1">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="35" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+      <c r="N14" s="85" t="n"/>
+      <c r="O14" s="85" t="n"/>
+    </row>
+    <row r="15" ht="34.5" customHeight="1">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="33" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
+      <c r="K15" s="85" t="n"/>
+      <c r="L15" s="85" t="n"/>
+      <c r="M15" s="85" t="n"/>
+      <c r="N15" s="85" t="n"/>
+      <c r="O15" s="85" t="n"/>
+    </row>
+    <row r="16" ht="34.5" customHeight="1">
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="33" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="35" t="n"/>
+      <c r="H16" s="85" t="n"/>
+      <c r="I16" s="85" t="n"/>
+      <c r="J16" s="85" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+      <c r="N16" s="85" t="n"/>
+      <c r="O16" s="85" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" thickBot="1">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B17" s="146" t="n"/>
-      <c r="C17" s="147" t="n"/>
-      <c r="D17" s="33">
+      <c r="B17" s="131" t="n"/>
+      <c r="C17" s="132" t="n"/>
+      <c r="D17" s="50">
         <f>SUM(D12:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="81" t="n"/>
-      <c r="G17" s="82" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="18" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" thickBot="1"/>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="98" t="inlineStr">
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="51" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="48" t="n"/>
+      <c r="I17" s="47" t="n"/>
+      <c r="J17" s="48" t="n"/>
+      <c r="K17" s="47" t="n"/>
+      <c r="L17" s="85" t="n"/>
+      <c r="M17" s="85" t="n"/>
+      <c r="N17" s="85" t="n"/>
+      <c r="O17" s="85" t="n"/>
+    </row>
+    <row r="18" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A18" s="85" t="n"/>
+      <c r="B18" s="85" t="n"/>
+      <c r="C18" s="85" t="n"/>
+      <c r="D18" s="85" t="n"/>
+      <c r="E18" s="85" t="n"/>
+      <c r="F18" s="85" t="n"/>
+      <c r="G18" s="85" t="n"/>
+      <c r="H18" s="85" t="n"/>
+      <c r="I18" s="85" t="n"/>
+      <c r="J18" s="85" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+      <c r="N18" s="85" t="n"/>
+      <c r="O18" s="85" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="89" t="inlineStr">
         <is>
           <t>ARSA MEVCUT DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B19" s="144" t="n"/>
-      <c r="C19" s="144" t="n"/>
-      <c r="D19" s="144" t="n"/>
-      <c r="E19" s="144" t="n"/>
-      <c r="F19" s="144" t="n"/>
-      <c r="G19" s="145" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
-    </row>
-    <row r="20" ht="35.25" customHeight="1">
-      <c r="A20" s="79" t="inlineStr">
+      <c r="B19" s="129" t="n"/>
+      <c r="C19" s="129" t="n"/>
+      <c r="D19" s="129" t="n"/>
+      <c r="E19" s="129" t="n"/>
+      <c r="F19" s="129" t="n"/>
+      <c r="G19" s="130" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
+      <c r="N19" s="85" t="n"/>
+      <c r="O19" s="85" t="n"/>
+    </row>
+    <row r="20" ht="70.5" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B20" s="76" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>ADA</t>
         </is>
       </c>
-      <c r="C20" s="75" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>PARSEL</t>
         </is>
       </c>
-      <c r="D20" s="76" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>YÜZÖLÇÜM
 (M²)</t>
         </is>
       </c>
-      <c r="E20" s="77" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>MEVCUT BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="F20" s="78" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve"> MEVCUT DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="G20" s="80" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="26" t="n"/>
-    </row>
-    <row r="21" ht="17.25" customHeight="1">
-      <c r="A21" s="121">
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="n"/>
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+    </row>
+    <row r="21" ht="34.5" customHeight="1">
+      <c r="A21" s="32">
         <f>A3</f>
         <v/>
       </c>
-      <c r="B21" s="122">
+      <c r="B21" s="33">
         <f>B3</f>
         <v/>
       </c>
-      <c r="C21" s="122">
+      <c r="C21" s="33">
         <f>C3</f>
         <v/>
       </c>
-      <c r="D21" s="122">
+      <c r="D21" s="33">
         <f>D3</f>
         <v/>
       </c>
-      <c r="E21" s="123">
+      <c r="E21" s="34">
         <f>F21/D21</f>
         <v/>
       </c>
-      <c r="F21" s="123">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="G21" s="3">
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>{{CURRENT_VALUE}}</t>
+        </is>
+      </c>
+      <c r="G21" s="35">
         <f>G12</f>
         <v/>
       </c>
-    </row>
-    <row r="22" ht="17.25" customHeight="1">
-      <c r="A22" s="121">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B22" s="122">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="C22" s="122">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D22" s="122">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E22" s="123">
-        <f>F22/D22</f>
-        <v/>
-      </c>
-      <c r="F22" s="123">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="G22" s="3">
-        <f>G13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="17.25" customHeight="1">
-      <c r="A23" s="121" t="n"/>
-      <c r="B23" s="122" t="n"/>
-      <c r="C23" s="122" t="n"/>
-      <c r="D23" s="122" t="n"/>
-      <c r="E23" s="123" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="17.25" customHeight="1">
-      <c r="A24" s="121" t="n"/>
-      <c r="B24" s="122" t="n"/>
-      <c r="C24" s="122" t="n"/>
-      <c r="D24" s="122" t="n"/>
-      <c r="E24" s="123" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="17.25" customHeight="1">
-      <c r="A25" s="121" t="n"/>
-      <c r="B25" s="122" t="n"/>
-      <c r="C25" s="122" t="n"/>
-      <c r="D25" s="122" t="n"/>
-      <c r="E25" s="123" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" thickBot="1">
-      <c r="A26" s="96" t="inlineStr">
+      <c r="H21" s="85" t="n"/>
+      <c r="I21" s="85" t="n"/>
+      <c r="J21" s="85" t="n"/>
+      <c r="K21" s="85" t="n"/>
+      <c r="L21" s="85" t="n"/>
+      <c r="M21" s="85" t="n"/>
+      <c r="N21" s="85" t="n"/>
+      <c r="O21" s="85" t="n"/>
+    </row>
+    <row r="22" ht="34.5" customHeight="1">
+      <c r="A22" s="32" t="n"/>
+      <c r="B22" s="33" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="85" t="n"/>
+      <c r="I22" s="85" t="n"/>
+      <c r="J22" s="85" t="n"/>
+      <c r="K22" s="85" t="n"/>
+      <c r="L22" s="85" t="n"/>
+      <c r="M22" s="85" t="n"/>
+      <c r="N22" s="85" t="n"/>
+      <c r="O22" s="85" t="n"/>
+    </row>
+    <row r="23" ht="34.5" customHeight="1">
+      <c r="A23" s="32" t="n"/>
+      <c r="B23" s="33" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="33" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="85" t="n"/>
+      <c r="I23" s="85" t="n"/>
+      <c r="J23" s="85" t="n"/>
+      <c r="K23" s="85" t="n"/>
+      <c r="L23" s="85" t="n"/>
+      <c r="M23" s="85" t="n"/>
+      <c r="N23" s="85" t="n"/>
+      <c r="O23" s="85" t="n"/>
+    </row>
+    <row r="24" ht="34.5" customHeight="1">
+      <c r="A24" s="32" t="n"/>
+      <c r="B24" s="33" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="n"/>
+      <c r="J24" s="85" t="n"/>
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="n"/>
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+    </row>
+    <row r="25" ht="34.5" customHeight="1">
+      <c r="A25" s="32" t="n"/>
+      <c r="B25" s="33" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="85" t="n"/>
+      <c r="I25" s="85" t="n"/>
+      <c r="J25" s="85" t="n"/>
+      <c r="K25" s="85" t="n"/>
+      <c r="L25" s="85" t="n"/>
+      <c r="M25" s="85" t="n"/>
+      <c r="N25" s="85" t="n"/>
+      <c r="O25" s="85" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" thickBot="1">
+      <c r="A26" s="72" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B26" s="146" t="n"/>
-      <c r="C26" s="147" t="n"/>
-      <c r="D26" s="33">
+      <c r="B26" s="131" t="n"/>
+      <c r="C26" s="132" t="n"/>
+      <c r="D26" s="50">
         <f>SUM(D21:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="33" t="n"/>
-      <c r="F26" s="81" t="n"/>
-      <c r="G26" s="82" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="18" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="95" t="n"/>
+      <c r="E26" s="50" t="n"/>
+      <c r="F26" s="51" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="48" t="n"/>
+      <c r="I26" s="47" t="n"/>
+      <c r="J26" s="48" t="n"/>
+      <c r="K26" s="47" t="n"/>
+      <c r="L26" s="85" t="n"/>
+      <c r="M26" s="85" t="n"/>
+      <c r="N26" s="85" t="n"/>
+      <c r="O26" s="85" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="84" t="n"/>
+      <c r="L27" s="85" t="n"/>
+      <c r="M27" s="85" t="n"/>
+      <c r="N27" s="85" t="n"/>
+      <c r="O27" s="85" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="N3:O5"/>
+  <mergeCells count="7">
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A27:K27"/>
   </mergeCells>
@@ -2556,299 +2658,320 @@
     <col width="14.85546875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="23.42578125" customWidth="1" style="1" min="3" max="3"/>
     <col width="36.85546875" customWidth="1" style="1" min="4" max="4"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="17" min="6" max="6"/>
-    <col width="16.5703125" customWidth="1" style="17" min="7" max="7"/>
+    <col width="22" customWidth="1" style="1" min="5" max="5"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
+    <col width="16.5703125" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A1" s="101" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" thickBot="1">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>KONUT - İŞYERLERİ YASAL DURUM DEĞERİ</t>
         </is>
       </c>
-      <c r="B1" s="142" t="n"/>
-      <c r="C1" s="142" t="n"/>
-      <c r="D1" s="142" t="n"/>
-      <c r="E1" s="142" t="n"/>
-      <c r="F1" s="142" t="n"/>
-      <c r="G1" s="143" t="n"/>
-    </row>
-    <row r="2" ht="30.75" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="B1" s="127" t="n"/>
+      <c r="C1" s="127" t="n"/>
+      <c r="D1" s="127" t="n"/>
+      <c r="E1" s="127" t="n"/>
+      <c r="F1" s="127" t="n"/>
+      <c r="G1" s="128" t="n"/>
+      <c r="H1" s="85" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="85" t="n"/>
+    </row>
+    <row r="2" ht="61.5" customFormat="1" customHeight="1" s="85" thickBot="1">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>GAYRİMENKUL 
 SIRA NO</t>
         </is>
       </c>
-      <c r="C2" s="45" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>GAYRİMENKUL ADI</t>
         </is>
       </c>
-      <c r="D2" s="45" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>YAPI RUHSATI/YKİB / YAPI KAYIT BELGESİ V.B YASAL EVRAK TARİH/SAYI</t>
         </is>
       </c>
-      <c r="E2" s="45" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>YASAL ALAN
 (M²)</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>YASAL BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="G2" s="51" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve"> YASAL DEĞER
 (TL)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="112" t="n">
+    <row r="3" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A3" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="113" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Sistemden BKNZ</t>
         </is>
       </c>
-      <c r="C3" s="113" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>{{GAYRIMENKUL_ADI}}</t>
         </is>
       </c>
-      <c r="D3" s="113" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
-      <c r="E3" s="113" t="n">
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>{{TOTAL_LEGAL_AREA}}</t>
+        </is>
+      </c>
+      <c r="F3" s="31">
+        <f>IFERROR(G3/E3,0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="114">
-        <f>IFERROR(G3/E3,0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="115" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="136" t="inlineStr">
+      <c r="H3" s="85" t="n"/>
+      <c r="I3" s="78" t="inlineStr">
         <is>
           <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
         </is>
       </c>
-      <c r="J3" s="137" t="n"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="121" t="n"/>
-      <c r="B4" s="122" t="n"/>
-      <c r="C4" s="122" t="n"/>
-      <c r="D4" s="122" t="n"/>
-      <c r="E4" s="122" t="n"/>
-      <c r="F4" s="123" t="n"/>
-      <c r="G4" s="124" t="n"/>
-      <c r="I4" s="138" t="n"/>
-      <c r="J4" s="139" t="n"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A5" s="121" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="122" t="n"/>
-      <c r="F5" s="123" t="n"/>
-      <c r="G5" s="124" t="n"/>
-      <c r="I5" s="140" t="n"/>
-      <c r="J5" s="141" t="n"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" thickBot="1">
-      <c r="A6" s="96" t="inlineStr">
+      <c r="J3" s="122" t="n"/>
+    </row>
+    <row r="4" ht="34.5" customHeight="1">
+      <c r="A4" s="32" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="85" t="n"/>
+      <c r="I4" s="123" t="n"/>
+      <c r="J4" s="124" t="n"/>
+    </row>
+    <row r="5" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A5" s="32" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="85" t="n"/>
+      <c r="I5" s="125" t="n"/>
+      <c r="J5" s="126" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" thickBot="1">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B6" s="146" t="n"/>
-      <c r="C6" s="146" t="n"/>
-      <c r="D6" s="147" t="n"/>
-      <c r="E6" s="97">
+      <c r="B6" s="131" t="n"/>
+      <c r="C6" s="131" t="n"/>
+      <c r="D6" s="132" t="n"/>
+      <c r="E6" s="55">
         <f>SUM(E3:E5)</f>
         <v/>
       </c>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34">
+      <c r="F6" s="50" t="n"/>
+      <c r="G6" s="56">
         <f>SUM(G3:G5)</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" thickBot="1"/>
-    <row r="8" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A8" s="83" t="inlineStr">
+      <c r="H6" s="85" t="n"/>
+      <c r="I6" s="85" t="n"/>
+      <c r="J6" s="85" t="n"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A7" s="85" t="n"/>
+      <c r="B7" s="85" t="n"/>
+      <c r="C7" s="85" t="n"/>
+      <c r="D7" s="85" t="n"/>
+      <c r="E7" s="85" t="n"/>
+      <c r="F7" s="85" t="n"/>
+      <c r="G7" s="85" t="n"/>
+      <c r="H7" s="85" t="n"/>
+      <c r="I7" s="85" t="n"/>
+      <c r="J7" s="85" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1" thickBot="1">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>KONUT - İŞYERLERİ MEVCUT DURUM DEĞERİ</t>
         </is>
       </c>
-      <c r="B8" s="134" t="n"/>
-      <c r="C8" s="134" t="n"/>
-      <c r="D8" s="134" t="n"/>
-      <c r="E8" s="134" t="n"/>
-      <c r="F8" s="134" t="n"/>
-      <c r="G8" s="135" t="n"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="B8" s="120" t="n"/>
+      <c r="C8" s="120" t="n"/>
+      <c r="D8" s="120" t="n"/>
+      <c r="E8" s="120" t="n"/>
+      <c r="F8" s="120" t="n"/>
+      <c r="G8" s="121" t="n"/>
+      <c r="H8" s="85" t="n"/>
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="n"/>
+    </row>
+    <row r="9" ht="61.5" customHeight="1" thickBot="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>GAYRİMENKUL 
 SIRA NO</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>GAYRİMENKUL ADI</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>YAPI RUHSATI/YKİB / YAPI KAYIT BELGESİ V.B YASAL EVRAK TARİH/SAYI</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>MEVCUT ALAN
 (M²)</t>
         </is>
       </c>
-      <c r="F9" s="42" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>MEVCUT BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve"> MEVCUT DEĞER
 (TL)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="A10" s="111" t="n">
+      <c r="H9" s="85" t="n"/>
+      <c r="I9" s="85" t="n"/>
+      <c r="J9" s="85" t="n"/>
+    </row>
+    <row r="10" ht="34.5" customHeight="1">
+      <c r="A10" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="116">
+      <c r="B10" s="58">
         <f>B3</f>
         <v/>
       </c>
-      <c r="C10" s="117">
+      <c r="C10" s="28">
         <f>C3</f>
         <v/>
       </c>
-      <c r="D10" s="118">
+      <c r="D10" s="29">
         <f>D3</f>
         <v/>
       </c>
-      <c r="E10" s="116" t="n">
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>{{TOTAL_CURRENT_AREA}}</t>
+        </is>
+      </c>
+      <c r="F10" s="31">
+        <f>IFERROR(G10/E10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="119">
-        <f>G10/E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="A11" s="121">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B11" s="122">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="C11" s="122">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D11" s="122" t="n"/>
-      <c r="E11" s="122">
-        <f>E4</f>
-        <v/>
-      </c>
-      <c r="F11" s="123" t="n"/>
-      <c r="G11" s="124" t="n"/>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="121">
-        <f>A5</f>
-        <v/>
-      </c>
-      <c r="B12" s="122">
-        <f>B5</f>
-        <v/>
-      </c>
-      <c r="C12" s="122">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="D12" s="122">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="E12" s="122">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="F12" s="123" t="n"/>
-      <c r="G12" s="124" t="n"/>
-    </row>
-    <row r="13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A13" s="125" t="n"/>
-      <c r="B13" s="126" t="n"/>
-      <c r="C13" s="126" t="n"/>
-      <c r="D13" s="126" t="n"/>
-      <c r="E13" s="126" t="n"/>
-      <c r="F13" s="127" t="n"/>
-      <c r="G13" s="128" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" thickBot="1">
-      <c r="A14" s="129" t="inlineStr">
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+    </row>
+    <row r="11" ht="34.5" customHeight="1">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="33" t="n"/>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="33" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="85" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="85" t="n"/>
+    </row>
+    <row r="12" ht="34.5" customHeight="1">
+      <c r="A12" s="32" t="n"/>
+      <c r="B12" s="33" t="n"/>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="85" t="n"/>
+      <c r="I12" s="85" t="n"/>
+      <c r="J12" s="85" t="n"/>
+    </row>
+    <row r="13" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A13" s="60" t="n"/>
+      <c r="B13" s="61" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="62" t="n"/>
+      <c r="G13" s="63" t="n"/>
+      <c r="H13" s="85" t="n"/>
+      <c r="I13" s="85" t="n"/>
+      <c r="J13" s="85" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" thickBot="1">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B14" s="148" t="n"/>
-      <c r="C14" s="148" t="n"/>
-      <c r="D14" s="148" t="n"/>
-      <c r="E14" s="131">
+      <c r="B14" s="133" t="n"/>
+      <c r="C14" s="133" t="n"/>
+      <c r="D14" s="133" t="n"/>
+      <c r="E14" s="64">
         <f>SUM(E10:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="132" t="n"/>
-      <c r="G14" s="133">
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="66">
         <f>SUM(G10:G13)</f>
         <v/>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="95" t="n"/>
+      <c r="H14" s="85" t="n"/>
+      <c r="I14" s="85" t="n"/>
+      <c r="J14" s="85" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="84" t="n"/>
+      <c r="H15" s="85" t="n"/>
+      <c r="I15" s="85" t="n"/>
+      <c r="J15" s="85" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2875,527 +2998,574 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.5703125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="14.85546875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15.85546875" customWidth="1" style="1" min="2" max="2"/>
     <col width="20.5703125" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
     <col width="12.42578125" customWidth="1" style="1" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
     <col width="41.42578125" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="14.140625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="21" bestFit="1" customWidth="1" style="17" min="8" max="8"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" style="17" min="9" max="9"/>
+    <col width="21" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
     <col width="15.5703125" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="45" customHeight="1" thickBot="1">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>NİTELİKLİ GAYRİMENKUL YASAL DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B1" s="134" t="n"/>
-      <c r="C1" s="134" t="n"/>
-      <c r="D1" s="134" t="n"/>
-      <c r="E1" s="134" t="n"/>
-      <c r="F1" s="134" t="n"/>
-      <c r="G1" s="134" t="n"/>
-      <c r="H1" s="134" t="n"/>
-      <c r="I1" s="134" t="n"/>
-      <c r="J1" s="135" t="n"/>
-    </row>
-    <row r="2" ht="35.25" customFormat="1" customHeight="1" s="12">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="B1" s="120" t="n"/>
+      <c r="C1" s="120" t="n"/>
+      <c r="D1" s="120" t="n"/>
+      <c r="E1" s="120" t="n"/>
+      <c r="F1" s="120" t="n"/>
+      <c r="G1" s="120" t="n"/>
+      <c r="H1" s="120" t="n"/>
+      <c r="I1" s="120" t="n"/>
+      <c r="J1" s="121" t="n"/>
+      <c r="K1" s="85" t="n"/>
+      <c r="L1" s="85" t="n"/>
+      <c r="M1" s="85" t="n"/>
+    </row>
+    <row r="2" ht="70.5" customFormat="1" customHeight="1" s="85">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>GAYRİMENKUL 
 SIRA NO</t>
         </is>
       </c>
-      <c r="C2" s="41" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>GAYİMENKUL ADI</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>YAPI SINIFI</t>
         </is>
       </c>
-      <c r="E2" s="41" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">KAT </t>
         </is>
       </c>
-      <c r="F2" s="40" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>YAPI RUHSATI/YKİB / YAPI KAYIT BELGESİ V.B YASAL EVRAK TARİH/SAYI</t>
         </is>
       </c>
-      <c r="G2" s="40" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>YASAL ALAN
 (M²)</t>
         </is>
       </c>
-      <c r="H2" s="42" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="I2" s="42" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> YASAL DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="J2" s="43" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A3" s="65" t="n">
+    <row r="3" ht="31.5" customFormat="1" customHeight="1" s="85">
+      <c r="A3" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="66" t="inlineStr">
+      <c r="B3" s="106" t="inlineStr">
         <is>
           <t>Sistemden BKNZ</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
-        <is>
-          <t>{{ANA_GAYRIMENKUL}}</t>
-        </is>
-      </c>
-      <c r="D3" s="68" t="n"/>
-      <c r="E3" s="67" t="inlineStr">
+      <c r="C3" s="112" t="inlineStr">
+        <is>
+          <t>ARSA</t>
+        </is>
+      </c>
+      <c r="D3" s="108" t="n"/>
+      <c r="E3" s="107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="66" t="inlineStr">
+      <c r="F3" s="106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="30">
+      <c r="G3" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_AREA}}</t>
+        </is>
+      </c>
+      <c r="H3" s="109">
         <f>I3/G3</f>
         <v/>
       </c>
-      <c r="I3" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="61" t="inlineStr">
-        <is>
-          <t>{{SATIS_KABILIYETI}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1">
-      <c r="A4" s="69" t="n">
+      <c r="I3" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J3" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34.5" customHeight="1">
+      <c r="A4" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="60" t="n">
-        <v>1234567</v>
-      </c>
-      <c r="C4" s="60" t="inlineStr">
-        <is>
-          <t>{{GAYRIMENKUL_ADI}}</t>
-        </is>
-      </c>
-      <c r="D4" s="70" t="inlineStr">
+      <c r="B4" s="107">
+        <f>+B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="112" t="inlineStr">
+        <is>
+          <t>YAPI DEĞERİ</t>
+        </is>
+      </c>
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>{{YAPI_SINIFI}}</t>
         </is>
       </c>
-      <c r="E4" s="60" t="inlineStr">
-        <is>
-          <t>{{KAT}}</t>
-        </is>
-      </c>
-      <c r="F4" s="60" t="inlineStr">
+      <c r="E4" s="112" t="inlineStr">
+        <is>
+          <t>{{MAİN_PROPERTY_FLOOR_COUNT_TEXT}}</t>
+        </is>
+      </c>
+      <c r="F4" s="107" t="inlineStr">
         <is>
           <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
-      <c r="G4" s="60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="30">
+      <c r="G4" s="114" t="inlineStr">
+        <is>
+          <t>{{TOTAL_LEGAL_AREA}}</t>
+        </is>
+      </c>
+      <c r="H4" s="109">
         <f>I4/G4</f>
         <v/>
       </c>
-      <c r="I4" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="62" t="inlineStr">
-        <is>
-          <t>{{SATIS_KABILIYETI}}</t>
-        </is>
-      </c>
-      <c r="L4" s="136" t="inlineStr">
-        <is>
-          <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
-        </is>
-      </c>
-      <c r="M4" s="137" t="n"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1">
-      <c r="A5" s="71" t="n"/>
-      <c r="B5" s="58" t="n"/>
-      <c r="C5" s="58" t="n"/>
-      <c r="D5" s="58" t="n"/>
-      <c r="E5" s="58" t="n"/>
-      <c r="F5" s="58" t="n"/>
-      <c r="G5" s="58" t="n"/>
-      <c r="H5" s="30">
-        <f>I5/G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="57" t="n"/>
-      <c r="J5" s="62" t="n"/>
-      <c r="L5" s="138" t="n"/>
-      <c r="M5" s="139" t="n"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A6" s="71" t="n"/>
-      <c r="B6" s="58" t="n"/>
-      <c r="C6" s="58" t="n"/>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="58" t="n"/>
-      <c r="F6" s="58" t="n"/>
-      <c r="G6" s="58" t="n"/>
-      <c r="H6" s="30">
-        <f>I6/G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="57" t="n"/>
-      <c r="J6" s="62" t="n"/>
-      <c r="L6" s="140" t="n"/>
-      <c r="M6" s="141" t="n"/>
-    </row>
-    <row r="7" ht="17.25" customHeight="1">
-      <c r="A7" s="121" t="n"/>
-      <c r="B7" s="122" t="n"/>
-      <c r="C7" s="122" t="n"/>
-      <c r="D7" s="122" t="n"/>
-      <c r="E7" s="122" t="n"/>
-      <c r="F7" s="122" t="n"/>
-      <c r="G7" s="122" t="n"/>
-      <c r="H7" s="123" t="n"/>
-      <c r="I7" s="123" t="n"/>
-      <c r="J7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="17.25" customHeight="1">
-      <c r="A8" s="121" t="n"/>
-      <c r="B8" s="122" t="n"/>
-      <c r="C8" s="122" t="n"/>
-      <c r="D8" s="122" t="n"/>
-      <c r="E8" s="122" t="n"/>
-      <c r="F8" s="122" t="n"/>
-      <c r="G8" s="122" t="n"/>
-      <c r="H8" s="123" t="n"/>
-      <c r="I8" s="123" t="n"/>
-      <c r="J8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" thickBot="1">
-      <c r="A9" s="149" t="inlineStr">
+      <c r="I4" s="116" t="inlineStr">
+        <is>
+          <t>{{LEGAL_BUİLDİNG_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J4" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="K4" s="85" t="n"/>
+    </row>
+    <row r="5" ht="34.5" customHeight="1">
+      <c r="A5" s="100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="101">
+        <f>+B4</f>
+        <v/>
+      </c>
+      <c r="C5" s="113" t="inlineStr">
+        <is>
+          <t>ŞEREFİYE VE ÇEVRE DÜZENLEMESİ</t>
+        </is>
+      </c>
+      <c r="D5" s="101" t="n"/>
+      <c r="E5" s="101" t="n"/>
+      <c r="F5" s="101" t="n"/>
+      <c r="G5" s="101" t="n"/>
+      <c r="H5" s="109" t="n"/>
+      <c r="I5" s="118" t="inlineStr">
+        <is>
+          <t>{{LEGAL_PREMİUM_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J5" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="K5" s="85" t="n"/>
+    </row>
+    <row r="6" ht="34.5" customHeight="1">
+      <c r="A6" s="100" t="n"/>
+      <c r="B6" s="101" t="n"/>
+      <c r="C6" s="101" t="n"/>
+      <c r="D6" s="101" t="n"/>
+      <c r="E6" s="101" t="n"/>
+      <c r="F6" s="101" t="n"/>
+      <c r="G6" s="101" t="n"/>
+      <c r="H6" s="109" t="n"/>
+      <c r="I6" s="102" t="n"/>
+      <c r="J6" s="111" t="n"/>
+      <c r="K6" s="85" t="n"/>
+    </row>
+    <row r="7" ht="34.5" customHeight="1">
+      <c r="A7" s="100" t="n"/>
+      <c r="B7" s="101" t="n"/>
+      <c r="C7" s="101" t="n"/>
+      <c r="D7" s="101" t="n"/>
+      <c r="E7" s="101" t="n"/>
+      <c r="F7" s="101" t="n"/>
+      <c r="G7" s="101" t="n"/>
+      <c r="H7" s="102" t="n"/>
+      <c r="I7" s="102" t="n"/>
+      <c r="J7" s="104" t="n"/>
+      <c r="K7" s="85" t="n"/>
+      <c r="L7" s="85" t="n"/>
+      <c r="M7" s="85" t="n"/>
+    </row>
+    <row r="8" ht="34.5" customHeight="1">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="35" t="n"/>
+      <c r="K8" s="85" t="n"/>
+      <c r="L8" s="85" t="n"/>
+      <c r="M8" s="85" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" thickBot="1">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B9" s="148" t="n"/>
-      <c r="C9" s="148" t="n"/>
-      <c r="D9" s="148" t="n"/>
-      <c r="E9" s="148" t="n"/>
-      <c r="F9" s="150" t="n"/>
-      <c r="G9" s="132">
+      <c r="B9" s="133" t="n"/>
+      <c r="C9" s="133" t="n"/>
+      <c r="D9" s="133" t="n"/>
+      <c r="E9" s="133" t="n"/>
+      <c r="F9" s="134" t="n"/>
+      <c r="G9" s="65">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="132" t="n"/>
-      <c r="I9" s="132">
+      <c r="H9" s="65" t="n"/>
+      <c r="I9" s="65">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="29" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" thickBot="1"/>
-    <row r="11" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="J9" s="67" t="n"/>
+      <c r="K9" s="85" t="n"/>
+      <c r="L9" s="85" t="n"/>
+      <c r="M9" s="85" t="n"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A10" s="85" t="n"/>
+      <c r="B10" s="85" t="n"/>
+      <c r="C10" s="85" t="n"/>
+      <c r="D10" s="85" t="n"/>
+      <c r="E10" s="85" t="n"/>
+      <c r="F10" s="85" t="n"/>
+      <c r="G10" s="85" t="n"/>
+      <c r="H10" s="85" t="n"/>
+      <c r="I10" s="85" t="n"/>
+      <c r="J10" s="85" t="n"/>
+      <c r="K10" s="85" t="n"/>
+      <c r="L10" s="85" t="n"/>
+      <c r="M10" s="85" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" thickBot="1">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t>NİTELİKLİ GAYRİMENKUL MEVCUT DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B11" s="134" t="n"/>
-      <c r="C11" s="134" t="n"/>
-      <c r="D11" s="134" t="n"/>
-      <c r="E11" s="134" t="n"/>
-      <c r="F11" s="134" t="n"/>
-      <c r="G11" s="134" t="n"/>
-      <c r="H11" s="134" t="n"/>
-      <c r="I11" s="134" t="n"/>
-      <c r="J11" s="135" t="n"/>
-    </row>
-    <row r="12" ht="35.25" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="B11" s="120" t="n"/>
+      <c r="C11" s="120" t="n"/>
+      <c r="D11" s="120" t="n"/>
+      <c r="E11" s="120" t="n"/>
+      <c r="F11" s="120" t="n"/>
+      <c r="G11" s="120" t="n"/>
+      <c r="H11" s="120" t="n"/>
+      <c r="I11" s="120" t="n"/>
+      <c r="J11" s="121" t="n"/>
+      <c r="K11" s="85" t="n"/>
+      <c r="L11" s="85" t="n"/>
+      <c r="M11" s="85" t="n"/>
+    </row>
+    <row r="12" ht="70.5" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SIRA NO</t>
         </is>
       </c>
-      <c r="B12" s="40" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>GAYRİMENKUL 
 SIRA NO</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>GAYRİMENKUL ADI</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>YAPI SINIFI</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>KAT</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>YAPI RUHSATI/YKİB / YAPI KAYIT BELGESİ V.B YASAL EVRAK TARİH/SAYI</t>
         </is>
       </c>
-      <c r="G12" s="40" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>MEVCUT ALAN
 (M²)</t>
         </is>
       </c>
-      <c r="H12" s="42" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>MEVCUT BİRİM DEĞER
 (TL/M²)</t>
         </is>
       </c>
-      <c r="I12" s="42" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> MEVCUT DEĞER
 (TL)</t>
         </is>
       </c>
-      <c r="J12" s="43" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>SATIŞ KABİLİYETİ</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="A13" s="35">
-        <f>A3</f>
-        <v/>
-      </c>
-      <c r="B13" s="36">
-        <f>B3</f>
-        <v/>
-      </c>
-      <c r="C13" s="36">
-        <f>C3</f>
-        <v/>
-      </c>
-      <c r="D13" s="59">
-        <f>D3</f>
-        <v/>
-      </c>
-      <c r="E13" s="36">
-        <f>E3</f>
-        <v/>
-      </c>
-      <c r="F13" s="36">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="G13" s="37">
-        <f>G3</f>
-        <v/>
-      </c>
-      <c r="H13" s="37">
+      <c r="K12" s="85" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+    </row>
+    <row r="13" ht="34.5" customHeight="1">
+      <c r="A13" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="106" t="inlineStr">
+        <is>
+          <t>Sistemden BKNZ</t>
+        </is>
+      </c>
+      <c r="C13" s="112" t="inlineStr">
+        <is>
+          <t>ARSA</t>
+        </is>
+      </c>
+      <c r="D13" s="108" t="n"/>
+      <c r="E13" s="107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_AREA}}</t>
+        </is>
+      </c>
+      <c r="H13" s="109">
         <f>I13/G13</f>
         <v/>
       </c>
-      <c r="I13" s="37">
-        <f>I3</f>
-        <v/>
-      </c>
-      <c r="J13" s="38">
-        <f>J3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="A14" s="35">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B14" s="36">
-        <f>B4</f>
-        <v/>
-      </c>
-      <c r="C14" s="36">
-        <f>C4</f>
-        <v/>
-      </c>
-      <c r="D14" s="59">
-        <f>D4</f>
-        <v/>
-      </c>
-      <c r="E14" s="36">
-        <f>E4</f>
-        <v/>
-      </c>
-      <c r="F14" s="36">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="G14" s="58" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" s="37">
+      <c r="I13" s="116" t="inlineStr">
+        <is>
+          <t>{{LAND_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J13" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="K13" s="85" t="n"/>
+      <c r="L13" s="85" t="n"/>
+      <c r="M13" s="85" t="n"/>
+    </row>
+    <row r="14" ht="34.5" customHeight="1">
+      <c r="A14" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="107">
+        <f>+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="112" t="inlineStr">
+        <is>
+          <t>YAPI DEĞERİ</t>
+        </is>
+      </c>
+      <c r="D14" s="110" t="inlineStr">
+        <is>
+          <t>{{YAPI_SINIFI}}</t>
+        </is>
+      </c>
+      <c r="E14" s="112" t="inlineStr">
+        <is>
+          <t>{{MAİN_PROPERTY_FLOOR_COUNT_TEXT}}</t>
+        </is>
+      </c>
+      <c r="F14" s="107" t="inlineStr">
+        <is>
+          <t>{{YAPI_BELGESI}}</t>
+        </is>
+      </c>
+      <c r="G14" s="114" t="inlineStr">
+        <is>
+          <t>{{TOTAL_CURRENT_AREA}}</t>
+        </is>
+      </c>
+      <c r="H14" s="109">
         <f>I14/G14</f>
         <v/>
       </c>
-      <c r="I14" s="64" t="n"/>
-      <c r="J14" s="38">
-        <f>J4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="A15" s="35">
-        <f>A5</f>
-        <v/>
-      </c>
-      <c r="B15" s="36">
-        <f>B5</f>
-        <v/>
-      </c>
-      <c r="C15" s="36">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="D15" s="59">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="E15" s="36">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="F15" s="36">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="G15" s="58" t="n"/>
-      <c r="H15" s="37">
-        <f>I15/G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="64" t="n"/>
-      <c r="J15" s="38">
-        <f>J5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="A16" s="35">
-        <f>A6</f>
-        <v/>
-      </c>
-      <c r="B16" s="36">
-        <f>B6</f>
-        <v/>
-      </c>
-      <c r="C16" s="36">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D16" s="59">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E16" s="36">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F16" s="36">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G16" s="58" t="n"/>
-      <c r="H16" s="37">
-        <f>I16/G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="64" t="n"/>
-      <c r="J16" s="38">
-        <f>J6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A17" s="121" t="n"/>
-      <c r="B17" s="122" t="n"/>
-      <c r="C17" s="122" t="n"/>
-      <c r="D17" s="122" t="n"/>
-      <c r="E17" s="122" t="n"/>
-      <c r="F17" s="122" t="n"/>
-      <c r="G17" s="122" t="n"/>
-      <c r="H17" s="123" t="n"/>
-      <c r="I17" s="114" t="n"/>
-      <c r="J17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" thickBot="1">
-      <c r="A18" s="105" t="inlineStr">
+      <c r="I14" s="116" t="inlineStr">
+        <is>
+          <t>{{CURRENT_BUİLDİNG_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J14" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="K14" s="85" t="n"/>
+      <c r="L14" s="85" t="n"/>
+      <c r="M14" s="85" t="n"/>
+    </row>
+    <row r="15" ht="34.5" customHeight="1">
+      <c r="A15" s="100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="101">
+        <f>+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="113" t="inlineStr">
+        <is>
+          <t>ŞEREFİYE VE ÇEVRE DÜZENLEMESİ</t>
+        </is>
+      </c>
+      <c r="D15" s="101" t="n"/>
+      <c r="E15" s="101" t="n"/>
+      <c r="F15" s="101" t="n"/>
+      <c r="G15" s="101" t="n"/>
+      <c r="H15" s="109" t="n"/>
+      <c r="I15" s="118" t="inlineStr">
+        <is>
+          <t>{{CURRENT_PREMİUM_VALUE}}</t>
+        </is>
+      </c>
+      <c r="J15" s="115" t="inlineStr">
+        <is>
+          <t>{{SALEABİLİTY}}</t>
+        </is>
+      </c>
+      <c r="K15" s="85" t="n"/>
+      <c r="L15" s="85" t="n"/>
+      <c r="M15" s="85" t="n"/>
+    </row>
+    <row r="16" ht="34.5" customHeight="1">
+      <c r="A16" s="105" t="n"/>
+      <c r="B16" s="107" t="n"/>
+      <c r="C16" s="107" t="n"/>
+      <c r="D16" s="110" t="n"/>
+      <c r="E16" s="107" t="n"/>
+      <c r="F16" s="107" t="n"/>
+      <c r="G16" s="101" t="n"/>
+      <c r="H16" s="117" t="n"/>
+      <c r="I16" s="117" t="n"/>
+      <c r="J16" s="111" t="n"/>
+      <c r="K16" s="85" t="n"/>
+      <c r="L16" s="85" t="n"/>
+      <c r="M16" s="85" t="n"/>
+    </row>
+    <row r="17" ht="34.5" customHeight="1" thickBot="1">
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="33" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="33" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="85" t="n"/>
+      <c r="L17" s="85" t="n"/>
+      <c r="M17" s="85" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" thickBot="1">
+      <c r="A18" s="92" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B18" s="134" t="n"/>
-      <c r="C18" s="134" t="n"/>
-      <c r="D18" s="134" t="n"/>
-      <c r="E18" s="135" t="n"/>
-      <c r="F18" s="106" t="n"/>
-      <c r="G18" s="106">
+      <c r="B18" s="120" t="n"/>
+      <c r="C18" s="120" t="n"/>
+      <c r="D18" s="120" t="n"/>
+      <c r="E18" s="121" t="n"/>
+      <c r="F18" s="46" t="n"/>
+      <c r="G18" s="46">
         <f>SUM(G13:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14">
+      <c r="H18" s="36" t="n"/>
+      <c r="I18" s="36">
         <f>SUM(I13:I17)</f>
         <v/>
       </c>
-      <c r="J18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="95" t="n"/>
+      <c r="J18" s="37" t="n"/>
+      <c r="K18" s="85" t="n"/>
+      <c r="L18" s="85" t="n"/>
+      <c r="M18" s="85" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="84" t="n"/>
+      <c r="K19" s="85" t="n"/>
+      <c r="L19" s="85" t="n"/>
+      <c r="M19" s="85" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="L4:M6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>

--- a/templates/ziraat-ek-tablo.xlsx
+++ b/templates/ziraat-ek-tablo.xlsx
@@ -689,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1050,6 +1050,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1057,11 +1060,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1635,12 +1653,12 @@
           <t>{{PARSEL}}</t>
         </is>
       </c>
-      <c r="D3" s="116" t="inlineStr">
+      <c r="D3" s="122" t="inlineStr">
         <is>
           <t>{{LAND_AREA}}</t>
         </is>
       </c>
-      <c r="E3" s="97">
+      <c r="E3" s="98">
         <f>F3/D3</f>
         <v/>
       </c>
@@ -1661,7 +1679,7 @@
           <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
         </is>
       </c>
-      <c r="K3" s="122" t="n"/>
+      <c r="K3" s="123" t="n"/>
     </row>
     <row r="4" ht="34.5" customHeight="1">
       <c r="A4" s="100" t="n"/>
@@ -1673,8 +1691,8 @@
       <c r="G4" s="104" t="n"/>
       <c r="H4" s="85" t="n"/>
       <c r="I4" s="85" t="n"/>
-      <c r="J4" s="123" t="n"/>
-      <c r="K4" s="124" t="n"/>
+      <c r="J4" s="124" t="n"/>
+      <c r="K4" s="125" t="n"/>
     </row>
     <row r="5" ht="34.5" customHeight="1" thickBot="1">
       <c r="A5" s="32" t="n"/>
@@ -1686,8 +1704,8 @@
       <c r="G5" s="35" t="n"/>
       <c r="H5" s="85" t="n"/>
       <c r="I5" s="85" t="n"/>
-      <c r="J5" s="125" t="n"/>
-      <c r="K5" s="126" t="n"/>
+      <c r="J5" s="126" t="n"/>
+      <c r="K5" s="127" t="n"/>
     </row>
     <row r="6" ht="34.5" customHeight="1">
       <c r="A6" s="32" t="n"/>
@@ -1723,7 +1741,7 @@
       </c>
       <c r="B8" s="120" t="n"/>
       <c r="C8" s="120" t="n"/>
-      <c r="D8" s="36">
+      <c r="D8" s="45">
         <f>SUM(D3:D7)</f>
         <v/>
       </c>
@@ -1826,11 +1844,11 @@
         <f>C3</f>
         <v/>
       </c>
-      <c r="D12" s="97">
+      <c r="D12" s="98">
         <f>D3</f>
         <v/>
       </c>
-      <c r="E12" s="97">
+      <c r="E12" s="98">
         <f>F12/D12</f>
         <v/>
       </c>
@@ -1909,7 +1927,7 @@
       </c>
       <c r="B17" s="120" t="n"/>
       <c r="C17" s="120" t="n"/>
-      <c r="D17" s="36">
+      <c r="D17" s="45">
         <f>SUM(D12:D16)</f>
         <v/>
       </c>
@@ -1974,16 +1992,16 @@
           <t>ARSA İMAR VE YAPILAŞMA KOŞULLARI</t>
         </is>
       </c>
-      <c r="B1" s="127" t="n"/>
-      <c r="C1" s="127" t="n"/>
-      <c r="D1" s="127" t="n"/>
-      <c r="E1" s="127" t="n"/>
-      <c r="F1" s="127" t="n"/>
-      <c r="G1" s="127" t="n"/>
-      <c r="H1" s="127" t="n"/>
-      <c r="I1" s="127" t="n"/>
-      <c r="J1" s="127" t="n"/>
-      <c r="K1" s="128" t="n"/>
+      <c r="B1" s="128" t="n"/>
+      <c r="C1" s="128" t="n"/>
+      <c r="D1" s="128" t="n"/>
+      <c r="E1" s="128" t="n"/>
+      <c r="F1" s="128" t="n"/>
+      <c r="G1" s="128" t="n"/>
+      <c r="H1" s="128" t="n"/>
+      <c r="I1" s="128" t="n"/>
+      <c r="J1" s="128" t="n"/>
+      <c r="K1" s="129" t="n"/>
       <c r="L1" s="85" t="n"/>
       <c r="M1" s="85" t="n"/>
       <c r="N1" s="85" t="n"/>
@@ -2066,7 +2084,7 @@
           <t>{{PARSEL}}</t>
         </is>
       </c>
-      <c r="D3" s="116" t="inlineStr">
+      <c r="D3" s="122" t="inlineStr">
         <is>
           <t>{{LAND_AREA}}</t>
         </is>
@@ -2082,7 +2100,7 @@
       <c r="G3" s="96" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="96" t="n">
+      <c r="H3" s="98" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="119" t="inlineStr">
@@ -2090,7 +2108,7 @@
           <t>{{CALCULATED_EMSAL}}</t>
         </is>
       </c>
-      <c r="J3" s="119" t="inlineStr">
+      <c r="J3" s="130" t="inlineStr">
         <is>
           <t>{{POST_ROAD_SETBACK_PARCEL_AREA}}</t>
         </is>
@@ -2173,7 +2191,7 @@
       </c>
       <c r="B8" s="120" t="n"/>
       <c r="C8" s="121" t="n"/>
-      <c r="D8" s="36">
+      <c r="D8" s="45">
         <f>SUM(D3:D7)</f>
         <v/>
       </c>
@@ -2212,12 +2230,12 @@
           <t>ARSA YASAL DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B10" s="129" t="n"/>
-      <c r="C10" s="129" t="n"/>
-      <c r="D10" s="129" t="n"/>
-      <c r="E10" s="129" t="n"/>
-      <c r="F10" s="129" t="n"/>
-      <c r="G10" s="130" t="n"/>
+      <c r="B10" s="131" t="n"/>
+      <c r="C10" s="131" t="n"/>
+      <c r="D10" s="131" t="n"/>
+      <c r="E10" s="131" t="n"/>
+      <c r="F10" s="131" t="n"/>
+      <c r="G10" s="132" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
@@ -2285,12 +2303,12 @@
         <f>C3</f>
         <v/>
       </c>
-      <c r="D12" s="116" t="inlineStr">
+      <c r="D12" s="122" t="inlineStr">
         <is>
           <t>{{LAND_AREA}}</t>
         </is>
       </c>
-      <c r="E12" s="102">
+      <c r="E12" s="103">
         <f>F12/D12</f>
         <v/>
       </c>
@@ -2387,9 +2405,9 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n"/>
-      <c r="C17" s="132" t="n"/>
-      <c r="D17" s="50">
+      <c r="B17" s="133" t="n"/>
+      <c r="C17" s="134" t="n"/>
+      <c r="D17" s="51">
         <f>SUM(D12:D16)</f>
         <v/>
       </c>
@@ -2428,12 +2446,12 @@
           <t>ARSA MEVCUT DURUM DEĞERİ/KANAAT TABLOSU</t>
         </is>
       </c>
-      <c r="B19" s="129" t="n"/>
-      <c r="C19" s="129" t="n"/>
-      <c r="D19" s="129" t="n"/>
-      <c r="E19" s="129" t="n"/>
-      <c r="F19" s="129" t="n"/>
-      <c r="G19" s="130" t="n"/>
+      <c r="B19" s="131" t="n"/>
+      <c r="C19" s="131" t="n"/>
+      <c r="D19" s="131" t="n"/>
+      <c r="E19" s="131" t="n"/>
+      <c r="F19" s="131" t="n"/>
+      <c r="G19" s="132" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
@@ -2504,11 +2522,11 @@
         <f>C3</f>
         <v/>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="39">
         <f>D3</f>
         <v/>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="39">
         <f>F21/D21</f>
         <v/>
       </c>
@@ -2604,9 +2622,9 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B26" s="131" t="n"/>
-      <c r="C26" s="132" t="n"/>
-      <c r="D26" s="50">
+      <c r="B26" s="133" t="n"/>
+      <c r="C26" s="134" t="n"/>
+      <c r="D26" s="51">
         <f>SUM(D21:D25)</f>
         <v/>
       </c>
@@ -2669,12 +2687,12 @@
           <t>KONUT - İŞYERLERİ YASAL DURUM DEĞERİ</t>
         </is>
       </c>
-      <c r="B1" s="127" t="n"/>
-      <c r="C1" s="127" t="n"/>
-      <c r="D1" s="127" t="n"/>
-      <c r="E1" s="127" t="n"/>
-      <c r="F1" s="127" t="n"/>
-      <c r="G1" s="128" t="n"/>
+      <c r="B1" s="128" t="n"/>
+      <c r="C1" s="128" t="n"/>
+      <c r="D1" s="128" t="n"/>
+      <c r="E1" s="128" t="n"/>
+      <c r="F1" s="128" t="n"/>
+      <c r="G1" s="129" t="n"/>
       <c r="H1" s="85" t="n"/>
       <c r="I1" s="85" t="n"/>
       <c r="J1" s="85" t="n"/>
@@ -2739,12 +2757,12 @@
           <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
-      <c r="E3" s="38" t="inlineStr">
+      <c r="E3" s="135" t="inlineStr">
         <is>
           <t>{{TOTAL_LEGAL_AREA}}</t>
         </is>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="135">
         <f>IFERROR(G3/E3,0)</f>
         <v/>
       </c>
@@ -2757,7 +2775,7 @@
           <t>SARI İLE BOYALI ALANLARA GİRİŞ YAPILMALIDIR</t>
         </is>
       </c>
-      <c r="J3" s="122" t="n"/>
+      <c r="J3" s="123" t="n"/>
     </row>
     <row r="4" ht="34.5" customHeight="1">
       <c r="A4" s="32" t="n"/>
@@ -2768,8 +2786,8 @@
       <c r="F4" s="34" t="n"/>
       <c r="G4" s="54" t="n"/>
       <c r="H4" s="85" t="n"/>
-      <c r="I4" s="123" t="n"/>
-      <c r="J4" s="124" t="n"/>
+      <c r="I4" s="124" t="n"/>
+      <c r="J4" s="125" t="n"/>
     </row>
     <row r="5" ht="34.5" customHeight="1" thickBot="1">
       <c r="A5" s="32" t="n"/>
@@ -2780,8 +2798,8 @@
       <c r="F5" s="34" t="n"/>
       <c r="G5" s="54" t="n"/>
       <c r="H5" s="85" t="n"/>
-      <c r="I5" s="125" t="n"/>
-      <c r="J5" s="126" t="n"/>
+      <c r="I5" s="126" t="n"/>
+      <c r="J5" s="127" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1" thickBot="1">
       <c r="A6" s="72" t="inlineStr">
@@ -2789,10 +2807,10 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n"/>
-      <c r="C6" s="131" t="n"/>
-      <c r="D6" s="132" t="n"/>
-      <c r="E6" s="55">
+      <c r="B6" s="133" t="n"/>
+      <c r="C6" s="133" t="n"/>
+      <c r="D6" s="134" t="n"/>
+      <c r="E6" s="51">
         <f>SUM(E3:E5)</f>
         <v/>
       </c>
@@ -2893,12 +2911,12 @@
         <f>D3</f>
         <v/>
       </c>
-      <c r="E10" s="58" t="inlineStr">
+      <c r="E10" s="136" t="inlineStr">
         <is>
           <t>{{TOTAL_CURRENT_AREA}}</t>
         </is>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="135">
         <f>IFERROR(G10/E10,0)</f>
         <v/>
       </c>
@@ -2951,10 +2969,10 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B14" s="133" t="n"/>
-      <c r="C14" s="133" t="n"/>
-      <c r="D14" s="133" t="n"/>
-      <c r="E14" s="64">
+      <c r="B14" s="137" t="n"/>
+      <c r="C14" s="137" t="n"/>
+      <c r="D14" s="137" t="n"/>
+      <c r="E14" s="138">
         <f>SUM(E10:E13)</f>
         <v/>
       </c>
@@ -3109,12 +3127,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="116" t="inlineStr">
+      <c r="G3" s="122" t="inlineStr">
         <is>
           <t>{{LAND_AREA}}</t>
         </is>
       </c>
-      <c r="H3" s="109">
+      <c r="H3" s="139">
         <f>I3/G3</f>
         <v/>
       </c>
@@ -3157,12 +3175,12 @@
           <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
-      <c r="G4" s="114" t="inlineStr">
+      <c r="G4" s="122" t="inlineStr">
         <is>
           <t>{{TOTAL_LEGAL_AREA}}</t>
         </is>
       </c>
-      <c r="H4" s="109">
+      <c r="H4" s="139">
         <f>I4/G4</f>
         <v/>
       </c>
@@ -3257,13 +3275,13 @@
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="B9" s="133" t="n"/>
-      <c r="C9" s="133" t="n"/>
-      <c r="D9" s="133" t="n"/>
-      <c r="E9" s="133" t="n"/>
-      <c r="F9" s="134" t="n"/>
-      <c r="G9" s="65">
-        <f>SUM(G3:G8)</f>
+      <c r="B9" s="137" t="n"/>
+      <c r="C9" s="137" t="n"/>
+      <c r="D9" s="137" t="n"/>
+      <c r="E9" s="137" t="n"/>
+      <c r="F9" s="140" t="n"/>
+      <c r="G9" s="138">
+        <f>SUM(G4:G8)</f>
         <v/>
       </c>
       <c r="H9" s="65" t="n"/>
@@ -3394,12 +3412,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="116" t="inlineStr">
+      <c r="G13" s="122" t="inlineStr">
         <is>
           <t>{{LAND_AREA}}</t>
         </is>
       </c>
-      <c r="H13" s="109">
+      <c r="H13" s="139">
         <f>I13/G13</f>
         <v/>
       </c>
@@ -3445,7 +3463,7 @@
           <t>{{YAPI_BELGESI}}</t>
         </is>
       </c>
-      <c r="G14" s="114" t="inlineStr">
+      <c r="G14" s="122" t="inlineStr">
         <is>
           <t>{{TOTAL_CURRENT_AREA}}</t>
         </is>
@@ -3541,8 +3559,8 @@
       <c r="D18" s="120" t="n"/>
       <c r="E18" s="121" t="n"/>
       <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46">
-        <f>SUM(G13:G17)</f>
+      <c r="G18" s="45">
+        <f>SUM(G14:G17)</f>
         <v/>
       </c>
       <c r="H18" s="36" t="n"/>
